--- a/GameDesign/策划文档/英雄技能设计.xlsx
+++ b/GameDesign/策划文档/英雄技能设计.xlsx
@@ -71,7 +71,7 @@
     <t>主动释放</t>
   </si>
   <si>
-    <t>对敌人造成350%物理伤害，如果敌人生命值低于30%，造成400%物理伤害；若成功击杀，将额外恢复50%的能量。</t>
+    <t>对敌人造成350%物理伤害，如果敌人生命值低于30%则伤害提升50%；若成功击杀，将额外恢复50%的能怒气。</t>
   </si>
   <si>
     <t>基础伤害</t>
@@ -107,7 +107,7 @@
     <t>战斗饥渴</t>
   </si>
   <si>
-    <t>每次攻击有概率对当前目标造成血量流失效果效果,使其每秒造成40%伤害,使其造成伤害降低20%，持续4秒。</t>
+    <t>每次攻击有概率对当前目标造成血量流失效果,使其每秒造成40%伤害,且造成伤害降低20%，持续4秒。</t>
   </si>
   <si>
     <t>大招单</t>
@@ -152,7 +152,7 @@
     <t>每次受到攻击有20%概率触发</t>
   </si>
   <si>
-    <t>提神自身的30%攻击速度和移动速度,并使自身的受到的伤害降低30%,持续5秒。</t>
+    <t>提升自身的30%攻击速度和移动速度,并使自身的受到的伤害降低30%,持续5秒。</t>
   </si>
   <si>
     <t>剑圣</t>

--- a/GameDesign/策划文档/英雄技能设计.xlsx
+++ b/GameDesign/策划文档/英雄技能设计.xlsx
@@ -200,7 +200,7 @@
     <t>在目标范围造成大面积持续伤害,每秒造成150%伤害,持续3秒。</t>
   </si>
   <si>
-    <t>冰霜新型</t>
+    <t>冰霜新星</t>
   </si>
   <si>
     <t>立即对目标及其周围的单位造成200%伤害,并且使其移动速度和攻击速度降低50%,持续4秒。</t>
@@ -297,7 +297,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -333,13 +333,6 @@
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -847,148 +840,148 @@
   </borders>
   <cellStyleXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
